--- a/WBS_Excel_V0.0_JP Example.xlsx
+++ b/WBS_Excel_V0.0_JP Example.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1216c861d618c7ef/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="229" documentId="8_{3E48023D-EB59-4BF6-81DB-BB99B990D1F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BCE29C0-148C-41C2-A8B8-91EA259D128D}"/>
+  <xr:revisionPtr revIDLastSave="232" documentId="8_{3E48023D-EB59-4BF6-81DB-BB99B990D1F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34701348-3170-49BC-A16E-5B73540721C4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{C13E4BC4-619E-4707-9B5C-4CBBCCD8F4CF}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="使い方ガイド" sheetId="5" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">WBS入力!$A$4:$L$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">WBS入力!$A$4:$K$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -811,7 +811,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -853,10 +853,10 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -871,7 +871,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -966,17 +965,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFA0A0A0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE0E0E0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF808080"/>
       </font>
       <fill>
@@ -1027,6 +1015,17 @@
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFA0A0A0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2083,45 +2082,35 @@
       <c r="J41" s="30"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L4" xr:uid="{790B7FA8-15DC-43F7-A7DD-AF0F8570FC3D}"/>
+  <autoFilter ref="A4:K4" xr:uid="{790B7FA8-15DC-43F7-A7DD-AF0F8570FC3D}"/>
   <phoneticPr fontId="16" type="noConversion"/>
-  <conditionalFormatting sqref="J5:K41">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
-      <formula>"完了"</formula>
+  <conditionalFormatting sqref="J5:J41">
+    <cfRule type="cellIs" dxfId="13" priority="6" operator="equal">
+      <formula>"中止"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J5:K41">
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+      <formula>"完了"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
       <formula>"進行中"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J5:K41">
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
       <formula>"遅延"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J5:K41">
-    <cfRule type="cellIs" dxfId="10" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="4" operator="equal">
       <formula>"保留"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J5:K41">
-    <cfRule type="cellIs" dxfId="9" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="5" operator="equal">
       <formula>"未着手"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J5:J41">
-    <cfRule type="cellIs" dxfId="8" priority="6" operator="equal">
-      <formula>"中止"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="入力エラー" error="リストから選択してください：未着手, 進行中, 完了, 遅延, 保留" promptTitle="ステータス" prompt="ドロップダウンから選択してください" sqref="K5:K41" xr:uid="{63B5A56D-E471-458D-9DF5-8CC8881B02DB}">
-      <formula1>"未着手,進行中,完了,遅延,保留"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="入力エラー" error="リストから選択してください：未着手, 進行中, 完了, 遅延, 保留, 中止" promptTitle="ステータス" prompt="ドロップダウンから選択してください" sqref="J5:J41" xr:uid="{464CC6E4-B570-49C4-A469-BECFD1047C12}">
       <formula1>"未着手,進行中,完了,遅延,保留,中止"</formula1>
     </dataValidation>
+    <dataValidation allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="リストから選択してください：未着手, 進行中, 完了, 遅延, 保留" sqref="K1:K1048576" xr:uid="{94129D52-1B3D-426C-932F-2A53CB306B6B}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2135,7 +2124,7 @@
     <col min="1" max="1" width="11.109375" customWidth="1"/>
     <col min="2" max="2" width="59.21875" customWidth="1"/>
     <col min="3" max="3" width="64.77734375" customWidth="1"/>
-    <col min="4" max="5" width="13" style="31" customWidth="1"/>
+    <col min="4" max="5" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.35">
@@ -2184,11 +2173,11 @@
         <f>IF(AND(WBS入力!A5="",WBS入力!B5=""),"",IF(WBS入力!A5&lt;&gt;"","",WBS入力!D5))</f>
         <v/>
       </c>
-      <c r="D5" s="32" t="str">
+      <c r="D5" s="31" t="str">
         <f>IF(AND(WBS入力!A5="",WBS入力!B5=""),"",IF(WBS入力!A5&lt;&gt;"","",IF(WBS入力!E5="","",WBS入力!E5)))</f>
         <v/>
       </c>
-      <c r="E5" s="32" t="str">
+      <c r="E5" s="31" t="str">
         <f>IF(AND(WBS入力!A5="",WBS入力!B5=""),"",IF(WBS入力!A5&lt;&gt;"","",IF(WBS入力!J5="","",WBS入力!J5)))</f>
         <v/>
       </c>
@@ -2206,11 +2195,11 @@
         <f>IF(AND(WBS入力!A6="",WBS入力!B6=""),"",IF(WBS入力!A6&lt;&gt;"","",WBS入力!D6))</f>
         <v>対象業務の範囲（スコープ）の明確化</v>
       </c>
-      <c r="D6" s="32" t="str">
+      <c r="D6" s="31" t="str">
         <f>IF(AND(WBS入力!A6="",WBS入力!B6=""),"",IF(WBS入力!A6&lt;&gt;"","",IF(WBS入力!E6="","",WBS入力!E6)))</f>
         <v>あおき</v>
       </c>
-      <c r="E6" s="32" t="str">
+      <c r="E6" s="31" t="str">
         <f>IF(AND(WBS入力!A6="",WBS入力!B6=""),"",IF(WBS入力!A6&lt;&gt;"","",IF(WBS入力!J6="","",WBS入力!J6)))</f>
         <v>進行中</v>
       </c>
@@ -2228,11 +2217,11 @@
         <f>IF(AND(WBS入力!A7="",WBS入力!B7=""),"",IF(WBS入力!A7&lt;&gt;"","",WBS入力!D7))</f>
         <v>給与・社保・勤怠のプロセスを最新化し可視化</v>
       </c>
-      <c r="D7" s="32" t="str">
+      <c r="D7" s="31" t="str">
         <f>IF(AND(WBS入力!A7="",WBS入力!B7=""),"",IF(WBS入力!A7&lt;&gt;"","",IF(WBS入力!E7="","",WBS入力!E7)))</f>
         <v>あおき</v>
       </c>
-      <c r="E7" s="32" t="str">
+      <c r="E7" s="31" t="str">
         <f>IF(AND(WBS入力!A7="",WBS入力!B7=""),"",IF(WBS入力!A7&lt;&gt;"","",IF(WBS入力!J7="","",WBS入力!J7)))</f>
         <v>進行中</v>
       </c>
@@ -2250,11 +2239,11 @@
         <f>IF(AND(WBS入力!A8="",WBS入力!B8=""),"",IF(WBS入力!A8&lt;&gt;"","",WBS入力!D8))</f>
         <v>現行ベンダーのパフォーマンスと未達項目の特定</v>
       </c>
-      <c r="D8" s="32" t="str">
+      <c r="D8" s="31" t="str">
         <f>IF(AND(WBS入力!A8="",WBS入力!B8=""),"",IF(WBS入力!A8&lt;&gt;"","",IF(WBS入力!E8="","",WBS入力!E8)))</f>
         <v>うえだ</v>
       </c>
-      <c r="E8" s="32" t="str">
+      <c r="E8" s="31" t="str">
         <f>IF(AND(WBS入力!A8="",WBS入力!B8=""),"",IF(WBS入力!A8&lt;&gt;"","",IF(WBS入力!J8="","",WBS入力!J8)))</f>
         <v>未着手</v>
       </c>
@@ -2272,11 +2261,11 @@
         <f>IF(AND(WBS入力!A9="",WBS入力!B9=""),"",IF(WBS入力!A9&lt;&gt;"","",WBS入力!D9))</f>
         <v>自社人事・IT部門・現行ベンダー間の責任範囲を整理</v>
       </c>
-      <c r="D9" s="32" t="str">
+      <c r="D9" s="31" t="str">
         <f>IF(AND(WBS入力!A9="",WBS入力!B9=""),"",IF(WBS入力!A9&lt;&gt;"","",IF(WBS入力!E9="","",WBS入力!E9)))</f>
         <v/>
       </c>
-      <c r="E9" s="32" t="str">
+      <c r="E9" s="31" t="str">
         <f>IF(AND(WBS入力!A9="",WBS入力!B9=""),"",IF(WBS入力!A9&lt;&gt;"","",IF(WBS入力!J9="","",WBS入力!J9)))</f>
         <v/>
       </c>
@@ -2294,11 +2283,11 @@
         <f>IF(AND(WBS入力!A10="",WBS入力!B10=""),"",IF(WBS入力!A10&lt;&gt;"","",WBS入力!D10))</f>
         <v>マニュアル化されていない特殊対応の特定</v>
       </c>
-      <c r="D10" s="32" t="str">
+      <c r="D10" s="31" t="str">
         <f>IF(AND(WBS入力!A10="",WBS入力!B10=""),"",IF(WBS入力!A10&lt;&gt;"","",IF(WBS入力!E10="","",WBS入力!E10)))</f>
         <v/>
       </c>
-      <c r="E10" s="32" t="str">
+      <c r="E10" s="31" t="str">
         <f>IF(AND(WBS入力!A10="",WBS入力!B10=""),"",IF(WBS入力!A10&lt;&gt;"","",IF(WBS入力!J10="","",WBS入力!J10)))</f>
         <v/>
       </c>
@@ -2316,11 +2305,11 @@
         <f>IF(AND(WBS入力!A11="",WBS入力!B11=""),"",IF(WBS入力!A11&lt;&gt;"","",WBS入力!D11))</f>
         <v>健康保険・厚生年金の取得/喪失、算定、月変の運用把握</v>
       </c>
-      <c r="D11" s="32" t="str">
+      <c r="D11" s="31" t="str">
         <f>IF(AND(WBS入力!A11="",WBS入力!B11=""),"",IF(WBS入力!A11&lt;&gt;"","",IF(WBS入力!E11="","",WBS入力!E11)))</f>
         <v/>
       </c>
-      <c r="E11" s="32" t="str">
+      <c r="E11" s="31" t="str">
         <f>IF(AND(WBS入力!A11="",WBS入力!B11=""),"",IF(WBS入力!A11&lt;&gt;"","",IF(WBS入力!J11="","",WBS入力!J11)))</f>
         <v/>
       </c>
@@ -2338,11 +2327,11 @@
         <f>IF(AND(WBS入力!A12="",WBS入力!B12=""),"",IF(WBS入力!A12&lt;&gt;"","",WBS入力!D12))</f>
         <v>退職金計算、離職票発行、育休・傷病手当運用の可視化</v>
       </c>
-      <c r="D12" s="32" t="str">
+      <c r="D12" s="31" t="str">
         <f>IF(AND(WBS入力!A12="",WBS入力!B12=""),"",IF(WBS入力!A12&lt;&gt;"","",IF(WBS入力!E12="","",WBS入力!E12)))</f>
         <v/>
       </c>
-      <c r="E12" s="32" t="str">
+      <c r="E12" s="31" t="str">
         <f>IF(AND(WBS入力!A12="",WBS入力!B12=""),"",IF(WBS入力!A12&lt;&gt;"","",IF(WBS入力!J12="","",WBS入力!J12)))</f>
         <v/>
       </c>
@@ -2360,11 +2349,11 @@
         <f>IF(AND(WBS入力!A13="",WBS入力!B13=""),"",IF(WBS入力!A13&lt;&gt;"","",WBS入力!D13))</f>
         <v>手当、持株会、財形、健康診断予約連携等の整理</v>
       </c>
-      <c r="D13" s="32" t="str">
+      <c r="D13" s="31" t="str">
         <f>IF(AND(WBS入力!A13="",WBS入力!B13=""),"",IF(WBS入力!A13&lt;&gt;"","",IF(WBS入力!E13="","",WBS入力!E13)))</f>
         <v/>
       </c>
-      <c r="E13" s="32" t="str">
+      <c r="E13" s="31" t="str">
         <f>IF(AND(WBS入力!A13="",WBS入力!B13=""),"",IF(WBS入力!A13&lt;&gt;"","",IF(WBS入力!J13="","",WBS入力!J13)))</f>
         <v/>
       </c>
@@ -2382,11 +2371,11 @@
         <f>IF(AND(WBS入力!A14="",WBS入力!B14=""),"",IF(WBS入力!A14&lt;&gt;"","",WBS入力!D14))</f>
         <v>スケジュール、申告システム、電子申請利用状況の特定</v>
       </c>
-      <c r="D14" s="32" t="str">
+      <c r="D14" s="31" t="str">
         <f>IF(AND(WBS入力!A14="",WBS入力!B14=""),"",IF(WBS入力!A14&lt;&gt;"","",IF(WBS入力!E14="","",WBS入力!E14)))</f>
         <v/>
       </c>
-      <c r="E14" s="32" t="str">
+      <c r="E14" s="31" t="str">
         <f>IF(AND(WBS入力!A14="",WBS入力!B14=""),"",IF(WBS入力!A14&lt;&gt;"","",IF(WBS入力!J14="","",WBS入力!J14)))</f>
         <v/>
       </c>
@@ -2404,11 +2393,11 @@
         <f>IF(AND(WBS入力!A15="",WBS入力!B15=""),"",IF(WBS入力!A15&lt;&gt;"","",WBS入力!D15))</f>
         <v>あいうえお</v>
       </c>
-      <c r="D15" s="32" t="str">
+      <c r="D15" s="31" t="str">
         <f>IF(AND(WBS入力!A15="",WBS入力!B15=""),"",IF(WBS入力!A15&lt;&gt;"","",IF(WBS入力!E15="","",WBS入力!E15)))</f>
         <v/>
       </c>
-      <c r="E15" s="32" t="str">
+      <c r="E15" s="31" t="str">
         <f>IF(AND(WBS入力!A15="",WBS入力!B15=""),"",IF(WBS入力!A15&lt;&gt;"","",IF(WBS入力!J15="","",WBS入力!J15)))</f>
         <v/>
       </c>
@@ -2426,11 +2415,11 @@
         <f>IF(AND(WBS入力!A16="",WBS入力!B16=""),"",IF(WBS入力!A16&lt;&gt;"","",WBS入力!D16))</f>
         <v>かきくけこ</v>
       </c>
-      <c r="D16" s="32" t="str">
+      <c r="D16" s="31" t="str">
         <f>IF(AND(WBS入力!A16="",WBS入力!B16=""),"",IF(WBS入力!A16&lt;&gt;"","",IF(WBS入力!E16="","",WBS入力!E16)))</f>
         <v/>
       </c>
-      <c r="E16" s="32" t="str">
+      <c r="E16" s="31" t="str">
         <f>IF(AND(WBS入力!A16="",WBS入力!B16=""),"",IF(WBS入力!A16&lt;&gt;"","",IF(WBS入力!J16="","",WBS入力!J16)))</f>
         <v/>
       </c>
@@ -2448,11 +2437,11 @@
         <f>IF(AND(WBS入力!A17="",WBS入力!B17=""),"",IF(WBS入力!A17&lt;&gt;"","",WBS入力!D17))</f>
         <v>プロジェクト実行計画の承認取得</v>
       </c>
-      <c r="D17" s="32" t="str">
+      <c r="D17" s="31" t="str">
         <f>IF(AND(WBS入力!A17="",WBS入力!B17=""),"",IF(WBS入力!A17&lt;&gt;"","",IF(WBS入力!E17="","",WBS入力!E17)))</f>
         <v/>
       </c>
-      <c r="E17" s="32" t="str">
+      <c r="E17" s="31" t="str">
         <f>IF(AND(WBS入力!A17="",WBS入力!B17=""),"",IF(WBS入力!A17&lt;&gt;"","",IF(WBS入力!J17="","",WBS入力!J17)))</f>
         <v/>
       </c>
@@ -2470,11 +2459,11 @@
         <f>IF(AND(WBS入力!A18="",WBS入力!B18=""),"",IF(WBS入力!A18&lt;&gt;"","",WBS入力!D18))</f>
         <v>初期導入費用とランニングコストの比較</v>
       </c>
-      <c r="D18" s="32" t="str">
+      <c r="D18" s="31" t="str">
         <f>IF(AND(WBS入力!A18="",WBS入力!B18=""),"",IF(WBS入力!A18&lt;&gt;"","",IF(WBS入力!E18="","",WBS入力!E18)))</f>
         <v/>
       </c>
-      <c r="E18" s="32" t="str">
+      <c r="E18" s="31" t="str">
         <f>IF(AND(WBS入力!A18="",WBS入力!B18=""),"",IF(WBS入力!A18&lt;&gt;"","",IF(WBS入力!J18="","",WBS入力!J18)))</f>
         <v/>
       </c>
@@ -2492,11 +2481,11 @@
         <f>IF(AND(WBS入力!A19="",WBS入力!B19=""),"",IF(WBS入力!A19&lt;&gt;"","",WBS入力!D19))</f>
         <v>RFP発行から本番稼働までの工程表作成</v>
       </c>
-      <c r="D19" s="32" t="str">
+      <c r="D19" s="31" t="str">
         <f>IF(AND(WBS入力!A19="",WBS入力!B19=""),"",IF(WBS入力!A19&lt;&gt;"","",IF(WBS入力!E19="","",WBS入力!E19)))</f>
         <v/>
       </c>
-      <c r="E19" s="32" t="str">
+      <c r="E19" s="31" t="str">
         <f>IF(AND(WBS入力!A19="",WBS入力!B19=""),"",IF(WBS入力!A19&lt;&gt;"","",IF(WBS入力!J19="","",WBS入力!J19)))</f>
         <v/>
       </c>
@@ -2514,11 +2503,11 @@
         <f>IF(AND(WBS入力!A20="",WBS入力!B20=""),"",IF(WBS入力!A20&lt;&gt;"","",WBS入力!D20))</f>
         <v>内部メンバーの工数確保と体制構築</v>
       </c>
-      <c r="D20" s="32" t="str">
+      <c r="D20" s="31" t="str">
         <f>IF(AND(WBS入力!A20="",WBS入力!B20=""),"",IF(WBS入力!A20&lt;&gt;"","",IF(WBS入力!E20="","",WBS入力!E20)))</f>
         <v/>
       </c>
-      <c r="E20" s="32" t="str">
+      <c r="E20" s="31" t="str">
         <f>IF(AND(WBS入力!A20="",WBS入力!B20=""),"",IF(WBS入力!A20&lt;&gt;"","",IF(WBS入力!J20="","",WBS入力!J20)))</f>
         <v/>
       </c>
@@ -2536,11 +2525,11 @@
         <f>IF(AND(WBS入力!A21="",WBS入力!B21=""),"",IF(WBS入力!A21&lt;&gt;"","",WBS入力!D21))</f>
         <v/>
       </c>
-      <c r="D21" s="32" t="str">
+      <c r="D21" s="31" t="str">
         <f>IF(AND(WBS入力!A21="",WBS入力!B21=""),"",IF(WBS入力!A21&lt;&gt;"","",IF(WBS入力!E21="","",WBS入力!E21)))</f>
         <v/>
       </c>
-      <c r="E21" s="32" t="str">
+      <c r="E21" s="31" t="str">
         <f>IF(AND(WBS入力!A21="",WBS入力!B21=""),"",IF(WBS入力!A21&lt;&gt;"","",IF(WBS入力!J21="","",WBS入力!J21)))</f>
         <v/>
       </c>
@@ -2558,11 +2547,11 @@
         <f>IF(AND(WBS入力!A22="",WBS入力!B22=""),"",IF(WBS入力!A22&lt;&gt;"","",WBS入力!D22))</f>
         <v>提案依頼書の送付と質疑応答</v>
       </c>
-      <c r="D22" s="32" t="str">
+      <c r="D22" s="31" t="str">
         <f>IF(AND(WBS入力!A22="",WBS入力!B22=""),"",IF(WBS入力!A22&lt;&gt;"","",IF(WBS入力!E22="","",WBS入力!E22)))</f>
         <v/>
       </c>
-      <c r="E22" s="32" t="str">
+      <c r="E22" s="31" t="str">
         <f>IF(AND(WBS入力!A22="",WBS入力!B22=""),"",IF(WBS入力!A22&lt;&gt;"","",IF(WBS入力!J22="","",WBS入力!J22)))</f>
         <v/>
       </c>
@@ -2580,11 +2569,11 @@
         <f>IF(AND(WBS入力!A23="",WBS入力!B23=""),"",IF(WBS入力!A23&lt;&gt;"","",WBS入力!D23))</f>
         <v>プレゼン実施とスコアリングによる決定</v>
       </c>
-      <c r="D23" s="32" t="str">
+      <c r="D23" s="31" t="str">
         <f>IF(AND(WBS入力!A23="",WBS入力!B23=""),"",IF(WBS入力!A23&lt;&gt;"","",IF(WBS入力!E23="","",WBS入力!E23)))</f>
         <v/>
       </c>
-      <c r="E23" s="32" t="str">
+      <c r="E23" s="31" t="str">
         <f>IF(AND(WBS入力!A23="",WBS入力!B23=""),"",IF(WBS入力!A23&lt;&gt;"","",IF(WBS入力!J23="","",WBS入力!J23)))</f>
         <v/>
       </c>
@@ -2602,11 +2591,11 @@
         <f>IF(AND(WBS入力!A24="",WBS入力!B24=""),"",IF(WBS入力!A24&lt;&gt;"","",WBS入力!D24))</f>
         <v/>
       </c>
-      <c r="D24" s="32" t="str">
+      <c r="D24" s="31" t="str">
         <f>IF(AND(WBS入力!A24="",WBS入力!B24=""),"",IF(WBS入力!A24&lt;&gt;"","",IF(WBS入力!E24="","",WBS入力!E24)))</f>
         <v/>
       </c>
-      <c r="E24" s="32" t="str">
+      <c r="E24" s="31" t="str">
         <f>IF(AND(WBS入力!A24="",WBS入力!B24=""),"",IF(WBS入力!A24&lt;&gt;"","",IF(WBS入力!J24="","",WBS入力!J24)))</f>
         <v/>
       </c>
@@ -2624,11 +2613,11 @@
         <f>IF(AND(WBS入力!A25="",WBS入力!B25=""),"",IF(WBS入力!A25&lt;&gt;"","",WBS入力!D25))</f>
         <v>新ベンダー体制での最適化</v>
       </c>
-      <c r="D25" s="32" t="str">
+      <c r="D25" s="31" t="str">
         <f>IF(AND(WBS入力!A25="",WBS入力!B25=""),"",IF(WBS入力!A25&lt;&gt;"","",IF(WBS入力!E25="","",WBS入力!E25)))</f>
         <v/>
       </c>
-      <c r="E25" s="32" t="str">
+      <c r="E25" s="31" t="str">
         <f>IF(AND(WBS入力!A25="",WBS入力!B25=""),"",IF(WBS入力!A25&lt;&gt;"","",IF(WBS入力!J25="","",WBS入力!J25)))</f>
         <v/>
       </c>
@@ -2646,11 +2635,11 @@
         <f>IF(AND(WBS入力!A26="",WBS入力!B26=""),"",IF(WBS入力!A26&lt;&gt;"","",WBS入力!D26))</f>
         <v>現行と新ベンダー標準機能の差分抽出</v>
       </c>
-      <c r="D26" s="32" t="str">
+      <c r="D26" s="31" t="str">
         <f>IF(AND(WBS入力!A26="",WBS入力!B26=""),"",IF(WBS入力!A26&lt;&gt;"","",IF(WBS入力!E26="","",WBS入力!E26)))</f>
         <v/>
       </c>
-      <c r="E26" s="32" t="str">
+      <c r="E26" s="31" t="str">
         <f>IF(AND(WBS入力!A26="",WBS入力!B26=""),"",IF(WBS入力!A26&lt;&gt;"","",IF(WBS入力!J26="","",WBS入力!J26)))</f>
         <v/>
       </c>
@@ -2668,11 +2657,11 @@
         <f>IF(AND(WBS入力!A27="",WBS入力!B27=""),"",IF(WBS入力!A27&lt;&gt;"","",WBS入力!D27))</f>
         <v>申請ルートとHRIS上の権限設定</v>
       </c>
-      <c r="D27" s="32" t="str">
+      <c r="D27" s="31" t="str">
         <f>IF(AND(WBS入力!A27="",WBS入力!B27=""),"",IF(WBS入力!A27&lt;&gt;"","",IF(WBS入力!E27="","",WBS入力!E27)))</f>
         <v/>
       </c>
-      <c r="E27" s="32" t="str">
+      <c r="E27" s="31" t="str">
         <f>IF(AND(WBS入力!A27="",WBS入力!B27=""),"",IF(WBS入力!A27&lt;&gt;"","",IF(WBS入力!J27="","",WBS入力!J27)))</f>
         <v/>
       </c>
@@ -2690,11 +2679,11 @@
         <f>IF(AND(WBS入力!A28="",WBS入力!B28=""),"",IF(WBS入力!A28&lt;&gt;"","",WBS入力!D28))</f>
         <v>データ整合性の担保</v>
       </c>
-      <c r="D28" s="32" t="str">
+      <c r="D28" s="31" t="str">
         <f>IF(AND(WBS入力!A28="",WBS入力!B28=""),"",IF(WBS入力!A28&lt;&gt;"","",IF(WBS入力!E28="","",WBS入力!E28)))</f>
         <v/>
       </c>
-      <c r="E28" s="32" t="str">
+      <c r="E28" s="31" t="str">
         <f>IF(AND(WBS入力!A28="",WBS入力!B28=""),"",IF(WBS入力!A28&lt;&gt;"","",IF(WBS入力!J28="","",WBS入力!J28)))</f>
         <v/>
       </c>
@@ -2712,11 +2701,11 @@
         <f>IF(AND(WBS入力!A29="",WBS入力!B29=""),"",IF(WBS入力!A29&lt;&gt;"","",WBS入力!D29))</f>
         <v>HCM, 給与システム等との連携項目定義</v>
       </c>
-      <c r="D29" s="32" t="str">
+      <c r="D29" s="31" t="str">
         <f>IF(AND(WBS入力!A29="",WBS入力!B29=""),"",IF(WBS入力!A29&lt;&gt;"","",IF(WBS入力!E29="","",WBS入力!E29)))</f>
         <v/>
       </c>
-      <c r="E29" s="32" t="str">
+      <c r="E29" s="31" t="str">
         <f>IF(AND(WBS入力!A29="",WBS入力!B29=""),"",IF(WBS入力!A29&lt;&gt;"","",IF(WBS入力!J29="","",WBS入力!J29)))</f>
         <v/>
       </c>
@@ -2734,11 +2723,11 @@
         <f>IF(AND(WBS入力!A30="",WBS入力!B30=""),"",IF(WBS入力!A30&lt;&gt;"","",WBS入力!D30))</f>
         <v>組織コード等の名称・属性の突合定義</v>
       </c>
-      <c r="D30" s="32" t="str">
+      <c r="D30" s="31" t="str">
         <f>IF(AND(WBS入力!A30="",WBS入力!B30=""),"",IF(WBS入力!A30&lt;&gt;"","",IF(WBS入力!E30="","",WBS入力!E30)))</f>
         <v/>
       </c>
-      <c r="E30" s="32" t="str">
+      <c r="E30" s="31" t="str">
         <f>IF(AND(WBS入力!A30="",WBS入力!B30=""),"",IF(WBS入力!A30&lt;&gt;"","",IF(WBS入力!J30="","",WBS入力!J30)))</f>
         <v/>
       </c>
@@ -2756,11 +2745,11 @@
         <f>IF(AND(WBS入力!A31="",WBS入力!B31=""),"",IF(WBS入力!A31&lt;&gt;"","",WBS入力!D31))</f>
         <v>切替リスクの最小化</v>
       </c>
-      <c r="D31" s="32" t="str">
+      <c r="D31" s="31" t="str">
         <f>IF(AND(WBS入力!A31="",WBS入力!B31=""),"",IF(WBS入力!A31&lt;&gt;"","",IF(WBS入力!E31="","",WBS入力!E31)))</f>
         <v/>
       </c>
-      <c r="E31" s="32" t="str">
+      <c r="E31" s="31" t="str">
         <f>IF(AND(WBS入力!A31="",WBS入力!B31=""),"",IF(WBS入力!A31&lt;&gt;"","",IF(WBS入力!J31="","",WBS入力!J31)))</f>
         <v/>
       </c>
@@ -2778,11 +2767,11 @@
         <f>IF(AND(WBS入力!A32="",WBS入力!B32=""),"",IF(WBS入力!A32&lt;&gt;"","",WBS入力!D32))</f>
         <v>移行前に修正が必要な人事情報の特定</v>
       </c>
-      <c r="D32" s="32" t="str">
+      <c r="D32" s="31" t="str">
         <f>IF(AND(WBS入力!A32="",WBS入力!B32=""),"",IF(WBS入力!A32&lt;&gt;"","",IF(WBS入力!E32="","",WBS入力!E32)))</f>
         <v/>
       </c>
-      <c r="E32" s="32" t="str">
+      <c r="E32" s="31" t="str">
         <f>IF(AND(WBS入力!A32="",WBS入力!B32=""),"",IF(WBS入力!A32&lt;&gt;"","",IF(WBS入力!J32="","",WBS入力!J32)))</f>
         <v/>
       </c>
@@ -2800,11 +2789,11 @@
         <f>IF(AND(WBS入力!A33="",WBS入力!B33=""),"",IF(WBS入力!A33&lt;&gt;"","",WBS入力!D33))</f>
         <v>給与計算の二重検証期間、検証対象者の策定</v>
       </c>
-      <c r="D33" s="32" t="str">
+      <c r="D33" s="31" t="str">
         <f>IF(AND(WBS入力!A33="",WBS入力!B33=""),"",IF(WBS入力!A33&lt;&gt;"","",IF(WBS入力!E33="","",WBS入力!E33)))</f>
         <v/>
       </c>
-      <c r="E33" s="32" t="str">
+      <c r="E33" s="31" t="str">
         <f>IF(AND(WBS入力!A33="",WBS入力!B33=""),"",IF(WBS入力!A33&lt;&gt;"","",IF(WBS入力!J33="","",WBS入力!J33)))</f>
         <v/>
       </c>
@@ -2822,11 +2811,11 @@
         <f>IF(AND(WBS入力!A34="",WBS入力!B34=""),"",IF(WBS入力!A34&lt;&gt;"","",WBS入力!D34))</f>
         <v/>
       </c>
-      <c r="D34" s="32" t="str">
+      <c r="D34" s="31" t="str">
         <f>IF(AND(WBS入力!A34="",WBS入力!B34=""),"",IF(WBS入力!A34&lt;&gt;"","",IF(WBS入力!E34="","",WBS入力!E34)))</f>
         <v/>
       </c>
-      <c r="E34" s="32" t="str">
+      <c r="E34" s="31" t="str">
         <f>IF(AND(WBS入力!A34="",WBS入力!B34=""),"",IF(WBS入力!A34&lt;&gt;"","",IF(WBS入力!J34="","",WBS入力!J34)))</f>
         <v/>
       </c>
@@ -2844,11 +2833,11 @@
         <f>IF(AND(WBS入力!A35="",WBS入力!B35=""),"",IF(WBS入力!A35&lt;&gt;"","",WBS入力!D35))</f>
         <v>業務シナリオに基づく運用テスト</v>
       </c>
-      <c r="D35" s="32" t="str">
+      <c r="D35" s="31" t="str">
         <f>IF(AND(WBS入力!A35="",WBS入力!B35=""),"",IF(WBS入力!A35&lt;&gt;"","",IF(WBS入力!E35="","",WBS入力!E35)))</f>
         <v/>
       </c>
-      <c r="E35" s="32" t="str">
+      <c r="E35" s="31" t="str">
         <f>IF(AND(WBS入力!A35="",WBS入力!B35=""),"",IF(WBS入力!A35&lt;&gt;"","",IF(WBS入力!J35="","",WBS入力!J35)))</f>
         <v/>
       </c>
@@ -2866,11 +2855,11 @@
         <f>IF(AND(WBS入力!A36="",WBS入力!B36=""),"",IF(WBS入力!A36&lt;&gt;"","",WBS入力!D36))</f>
         <v/>
       </c>
-      <c r="D36" s="32" t="str">
+      <c r="D36" s="31" t="str">
         <f>IF(AND(WBS入力!A36="",WBS入力!B36=""),"",IF(WBS入力!A36&lt;&gt;"","",IF(WBS入力!E36="","",WBS入力!E36)))</f>
         <v/>
       </c>
-      <c r="E36" s="32" t="str">
+      <c r="E36" s="31" t="str">
         <f>IF(AND(WBS入力!A36="",WBS入力!B36=""),"",IF(WBS入力!A36&lt;&gt;"","",IF(WBS入力!J36="","",WBS入力!J36)))</f>
         <v/>
       </c>
@@ -2888,11 +2877,11 @@
         <f>IF(AND(WBS入力!A37="",WBS入力!B37=""),"",IF(WBS入力!A37&lt;&gt;"","",WBS入力!D37))</f>
         <v>現行と新ベンダーによる給与計算の突合</v>
       </c>
-      <c r="D37" s="32" t="str">
+      <c r="D37" s="31" t="str">
         <f>IF(AND(WBS入力!A37="",WBS入力!B37=""),"",IF(WBS入力!A37&lt;&gt;"","",IF(WBS入力!E37="","",WBS入力!E37)))</f>
         <v/>
       </c>
-      <c r="E37" s="32" t="str">
+      <c r="E37" s="31" t="str">
         <f>IF(AND(WBS入力!A37="",WBS入力!B37=""),"",IF(WBS入力!A37&lt;&gt;"","",IF(WBS入力!J37="","",WBS入力!J37)))</f>
         <v/>
       </c>
@@ -2910,11 +2899,11 @@
         <f>IF(AND(WBS入力!A38="",WBS入力!B38=""),"",IF(WBS入力!A38&lt;&gt;"","",WBS入力!D38))</f>
         <v>新ベンダーへの完全移行</v>
       </c>
-      <c r="D38" s="32" t="str">
+      <c r="D38" s="31" t="str">
         <f>IF(AND(WBS入力!A38="",WBS入力!B38=""),"",IF(WBS入力!A38&lt;&gt;"","",IF(WBS入力!E38="","",WBS入力!E38)))</f>
         <v/>
       </c>
-      <c r="E38" s="32" t="str">
+      <c r="E38" s="31" t="str">
         <f>IF(AND(WBS入力!A38="",WBS入力!B38=""),"",IF(WBS入力!A38&lt;&gt;"","",IF(WBS入力!J38="","",WBS入力!J38)))</f>
         <v/>
       </c>
@@ -2932,11 +2921,11 @@
         <f>IF(AND(WBS入力!A39="",WBS入力!B39=""),"",IF(WBS入力!A39&lt;&gt;"","",WBS入力!D39))</f>
         <v/>
       </c>
-      <c r="D39" s="32" t="str">
+      <c r="D39" s="31" t="str">
         <f>IF(AND(WBS入力!A39="",WBS入力!B39=""),"",IF(WBS入力!A39&lt;&gt;"","",IF(WBS入力!E39="","",WBS入力!E39)))</f>
         <v/>
       </c>
-      <c r="E39" s="32" t="str">
+      <c r="E39" s="31" t="str">
         <f>IF(AND(WBS入力!A39="",WBS入力!B39=""),"",IF(WBS入力!A39&lt;&gt;"","",IF(WBS入力!J39="","",WBS入力!J39)))</f>
         <v/>
       </c>
@@ -2954,11 +2943,11 @@
         <f>IF(AND(WBS入力!A40="",WBS入力!B40=""),"",IF(WBS入力!A40&lt;&gt;"","",WBS入力!D40))</f>
         <v>あいうえお</v>
       </c>
-      <c r="D40" s="32" t="str">
+      <c r="D40" s="31" t="str">
         <f>IF(AND(WBS入力!A40="",WBS入力!B40=""),"",IF(WBS入力!A40&lt;&gt;"","",IF(WBS入力!E40="","",WBS入力!E40)))</f>
         <v/>
       </c>
-      <c r="E40" s="32" t="str">
+      <c r="E40" s="31" t="str">
         <f>IF(AND(WBS入力!A40="",WBS入力!B40=""),"",IF(WBS入力!A40&lt;&gt;"","",IF(WBS入力!J40="","",WBS入力!J40)))</f>
         <v/>
       </c>
@@ -2976,11 +2965,11 @@
         <f>IF(AND(WBS入力!A41="",WBS入力!B41=""),"",IF(WBS入力!A41&lt;&gt;"","",WBS入力!D41))</f>
         <v>かきくけこ</v>
       </c>
-      <c r="D41" s="32" t="str">
+      <c r="D41" s="31" t="str">
         <f>IF(AND(WBS入力!A41="",WBS入力!B41=""),"",IF(WBS入力!A41&lt;&gt;"","",IF(WBS入力!E41="","",WBS入力!E41)))</f>
         <v/>
       </c>
-      <c r="E41" s="32" t="str">
+      <c r="E41" s="31" t="str">
         <f>IF(AND(WBS入力!A41="",WBS入力!B41=""),"",IF(WBS入力!A41&lt;&gt;"","",IF(WBS入力!J41="","",WBS入力!J41)))</f>
         <v/>
       </c>
@@ -2998,11 +2987,11 @@
         <f>IF(AND(WBS入力!A42="",WBS入力!B42=""),"",IF(WBS入力!A42&lt;&gt;"","",WBS入力!D42))</f>
         <v/>
       </c>
-      <c r="D42" s="32" t="str">
+      <c r="D42" s="31" t="str">
         <f>IF(AND(WBS入力!A42="",WBS入力!B42=""),"",IF(WBS入力!A42&lt;&gt;"","",IF(WBS入力!E42="","",WBS入力!E42)))</f>
         <v/>
       </c>
-      <c r="E42" s="32" t="str">
+      <c r="E42" s="31" t="str">
         <f>IF(AND(WBS入力!A42="",WBS入力!B42=""),"",IF(WBS入力!A42&lt;&gt;"","",IF(WBS入力!J42="","",WBS入力!J42)))</f>
         <v/>
       </c>
@@ -3020,11 +3009,11 @@
         <f>IF(AND(WBS入力!A43="",WBS入力!B43=""),"",IF(WBS入力!A43&lt;&gt;"","",WBS入力!D43))</f>
         <v/>
       </c>
-      <c r="D43" s="32" t="str">
+      <c r="D43" s="31" t="str">
         <f>IF(AND(WBS入力!A43="",WBS入力!B43=""),"",IF(WBS入力!A43&lt;&gt;"","",IF(WBS入力!E43="","",WBS入力!E43)))</f>
         <v/>
       </c>
-      <c r="E43" s="32" t="str">
+      <c r="E43" s="31" t="str">
         <f>IF(AND(WBS入力!A43="",WBS入力!B43=""),"",IF(WBS入力!A43&lt;&gt;"","",IF(WBS入力!J43="","",WBS入力!J43)))</f>
         <v/>
       </c>
@@ -3042,11 +3031,11 @@
         <f>IF(AND(WBS入力!A44="",WBS入力!B44=""),"",IF(WBS入力!A44&lt;&gt;"","",WBS入力!D44))</f>
         <v/>
       </c>
-      <c r="D44" s="32" t="str">
+      <c r="D44" s="31" t="str">
         <f>IF(AND(WBS入力!A44="",WBS入力!B44=""),"",IF(WBS入力!A44&lt;&gt;"","",IF(WBS入力!E44="","",WBS入力!E44)))</f>
         <v/>
       </c>
-      <c r="E44" s="32" t="str">
+      <c r="E44" s="31" t="str">
         <f>IF(AND(WBS入力!A44="",WBS入力!B44=""),"",IF(WBS入力!A44&lt;&gt;"","",IF(WBS入力!J44="","",WBS入力!J44)))</f>
         <v/>
       </c>
@@ -3064,11 +3053,11 @@
         <f>IF(AND(WBS入力!A45="",WBS入力!B45=""),"",IF(WBS入力!A45&lt;&gt;"","",WBS入力!D45))</f>
         <v/>
       </c>
-      <c r="D45" s="32" t="str">
+      <c r="D45" s="31" t="str">
         <f>IF(AND(WBS入力!A45="",WBS入力!B45=""),"",IF(WBS入力!A45&lt;&gt;"","",IF(WBS入力!E45="","",WBS入力!E45)))</f>
         <v/>
       </c>
-      <c r="E45" s="32" t="str">
+      <c r="E45" s="31" t="str">
         <f>IF(AND(WBS入力!A45="",WBS入力!B45=""),"",IF(WBS入力!A45&lt;&gt;"","",IF(WBS入力!J45="","",WBS入力!J45)))</f>
         <v/>
       </c>
@@ -3086,11 +3075,11 @@
         <f>IF(AND(WBS入力!A46="",WBS入力!B46=""),"",IF(WBS入力!A46&lt;&gt;"","",WBS入力!D46))</f>
         <v/>
       </c>
-      <c r="D46" s="32" t="str">
+      <c r="D46" s="31" t="str">
         <f>IF(AND(WBS入力!A46="",WBS入力!B46=""),"",IF(WBS入力!A46&lt;&gt;"","",IF(WBS入力!E46="","",WBS入力!E46)))</f>
         <v/>
       </c>
-      <c r="E46" s="32" t="str">
+      <c r="E46" s="31" t="str">
         <f>IF(AND(WBS入力!A46="",WBS入力!B46=""),"",IF(WBS入力!A46&lt;&gt;"","",IF(WBS入力!J46="","",WBS入力!J46)))</f>
         <v/>
       </c>
@@ -3108,11 +3097,11 @@
         <f>IF(AND(WBS入力!A47="",WBS入力!B47=""),"",IF(WBS入力!A47&lt;&gt;"","",WBS入力!D47))</f>
         <v/>
       </c>
-      <c r="D47" s="32" t="str">
+      <c r="D47" s="31" t="str">
         <f>IF(AND(WBS入力!A47="",WBS入力!B47=""),"",IF(WBS入力!A47&lt;&gt;"","",IF(WBS入力!E47="","",WBS入力!E47)))</f>
         <v/>
       </c>
-      <c r="E47" s="32" t="str">
+      <c r="E47" s="31" t="str">
         <f>IF(AND(WBS入力!A47="",WBS入力!B47=""),"",IF(WBS入力!A47&lt;&gt;"","",IF(WBS入力!J47="","",WBS入力!J47)))</f>
         <v/>
       </c>
@@ -3130,11 +3119,11 @@
         <f>IF(AND(WBS入力!A48="",WBS入力!B48=""),"",IF(WBS入力!A48&lt;&gt;"","",WBS入力!D48))</f>
         <v/>
       </c>
-      <c r="D48" s="32" t="str">
+      <c r="D48" s="31" t="str">
         <f>IF(AND(WBS入力!A48="",WBS入力!B48=""),"",IF(WBS入力!A48&lt;&gt;"","",IF(WBS入力!E48="","",WBS入力!E48)))</f>
         <v/>
       </c>
-      <c r="E48" s="32" t="str">
+      <c r="E48" s="31" t="str">
         <f>IF(AND(WBS入力!A48="",WBS入力!B48=""),"",IF(WBS入力!A48&lt;&gt;"","",IF(WBS入力!J48="","",WBS入力!J48)))</f>
         <v/>
       </c>
@@ -3152,11 +3141,11 @@
         <f>IF(AND(WBS入力!A49="",WBS入力!B49=""),"",IF(WBS入力!A49&lt;&gt;"","",WBS入力!D49))</f>
         <v/>
       </c>
-      <c r="D49" s="32" t="str">
+      <c r="D49" s="31" t="str">
         <f>IF(AND(WBS入力!A49="",WBS入力!B49=""),"",IF(WBS入力!A49&lt;&gt;"","",IF(WBS入力!E49="","",WBS入力!E49)))</f>
         <v/>
       </c>
-      <c r="E49" s="32" t="str">
+      <c r="E49" s="31" t="str">
         <f>IF(AND(WBS入力!A49="",WBS入力!B49=""),"",IF(WBS入力!A49&lt;&gt;"","",IF(WBS入力!J49="","",WBS入力!J49)))</f>
         <v/>
       </c>
@@ -3174,11 +3163,11 @@
         <f>IF(AND(WBS入力!A50="",WBS入力!B50=""),"",IF(WBS入力!A50&lt;&gt;"","",WBS入力!D50))</f>
         <v/>
       </c>
-      <c r="D50" s="32" t="str">
+      <c r="D50" s="31" t="str">
         <f>IF(AND(WBS入力!A50="",WBS入力!B50=""),"",IF(WBS入力!A50&lt;&gt;"","",IF(WBS入力!E50="","",WBS入力!E50)))</f>
         <v/>
       </c>
-      <c r="E50" s="32" t="str">
+      <c r="E50" s="31" t="str">
         <f>IF(AND(WBS入力!A50="",WBS入力!B50=""),"",IF(WBS入力!A50&lt;&gt;"","",IF(WBS入力!J50="","",WBS入力!J50)))</f>
         <v/>
       </c>
@@ -3196,11 +3185,11 @@
         <f>IF(AND(WBS入力!A51="",WBS入力!B51=""),"",IF(WBS入力!A51&lt;&gt;"","",WBS入力!D51))</f>
         <v/>
       </c>
-      <c r="D51" s="32" t="str">
+      <c r="D51" s="31" t="str">
         <f>IF(AND(WBS入力!A51="",WBS入力!B51=""),"",IF(WBS入力!A51&lt;&gt;"","",IF(WBS入力!E51="","",WBS入力!E51)))</f>
         <v/>
       </c>
-      <c r="E51" s="32" t="str">
+      <c r="E51" s="31" t="str">
         <f>IF(AND(WBS入力!A51="",WBS入力!B51=""),"",IF(WBS入力!A51&lt;&gt;"","",IF(WBS入力!J51="","",WBS入力!J51)))</f>
         <v/>
       </c>
@@ -3218,11 +3207,11 @@
         <f>IF(AND(WBS入力!A52="",WBS入力!B52=""),"",IF(WBS入力!A52&lt;&gt;"","",WBS入力!D52))</f>
         <v/>
       </c>
-      <c r="D52" s="32" t="str">
+      <c r="D52" s="31" t="str">
         <f>IF(AND(WBS入力!A52="",WBS入力!B52=""),"",IF(WBS入力!A52&lt;&gt;"","",IF(WBS入力!E52="","",WBS入力!E52)))</f>
         <v/>
       </c>
-      <c r="E52" s="32" t="str">
+      <c r="E52" s="31" t="str">
         <f>IF(AND(WBS入力!A52="",WBS入力!B52=""),"",IF(WBS入力!A52&lt;&gt;"","",IF(WBS入力!J52="","",WBS入力!J52)))</f>
         <v/>
       </c>
@@ -3240,11 +3229,11 @@
         <f>IF(AND(WBS入力!A53="",WBS入力!B53=""),"",IF(WBS入力!A53&lt;&gt;"","",WBS入力!D53))</f>
         <v/>
       </c>
-      <c r="D53" s="32" t="str">
+      <c r="D53" s="31" t="str">
         <f>IF(AND(WBS入力!A53="",WBS入力!B53=""),"",IF(WBS入力!A53&lt;&gt;"","",IF(WBS入力!E53="","",WBS入力!E53)))</f>
         <v/>
       </c>
-      <c r="E53" s="32" t="str">
+      <c r="E53" s="31" t="str">
         <f>IF(AND(WBS入力!A53="",WBS入力!B53=""),"",IF(WBS入力!A53&lt;&gt;"","",IF(WBS入力!J53="","",WBS入力!J53)))</f>
         <v/>
       </c>
@@ -3262,11 +3251,11 @@
         <f>IF(AND(WBS入力!A54="",WBS入力!B54=""),"",IF(WBS入力!A54&lt;&gt;"","",WBS入力!D54))</f>
         <v/>
       </c>
-      <c r="D54" s="32" t="str">
+      <c r="D54" s="31" t="str">
         <f>IF(AND(WBS入力!A54="",WBS入力!B54=""),"",IF(WBS入力!A54&lt;&gt;"","",IF(WBS入力!E54="","",WBS入力!E54)))</f>
         <v/>
       </c>
-      <c r="E54" s="32" t="str">
+      <c r="E54" s="31" t="str">
         <f>IF(AND(WBS入力!A54="",WBS入力!B54=""),"",IF(WBS入力!A54&lt;&gt;"","",IF(WBS入力!J54="","",WBS入力!J54)))</f>
         <v/>
       </c>
@@ -3284,11 +3273,11 @@
         <f>IF(AND(WBS入力!A55="",WBS入力!B55=""),"",IF(WBS入力!A55&lt;&gt;"","",WBS入力!D55))</f>
         <v/>
       </c>
-      <c r="D55" s="32" t="str">
+      <c r="D55" s="31" t="str">
         <f>IF(AND(WBS入力!A55="",WBS入力!B55=""),"",IF(WBS入力!A55&lt;&gt;"","",IF(WBS入力!E55="","",WBS入力!E55)))</f>
         <v/>
       </c>
-      <c r="E55" s="32" t="str">
+      <c r="E55" s="31" t="str">
         <f>IF(AND(WBS入力!A55="",WBS入力!B55=""),"",IF(WBS入力!A55&lt;&gt;"","",IF(WBS入力!J55="","",WBS入力!J55)))</f>
         <v/>
       </c>
@@ -3306,11 +3295,11 @@
         <f>IF(AND(WBS入力!A56="",WBS入力!B56=""),"",IF(WBS入力!A56&lt;&gt;"","",WBS入力!D56))</f>
         <v/>
       </c>
-      <c r="D56" s="32" t="str">
+      <c r="D56" s="31" t="str">
         <f>IF(AND(WBS入力!A56="",WBS入力!B56=""),"",IF(WBS入力!A56&lt;&gt;"","",IF(WBS入力!E56="","",WBS入力!E56)))</f>
         <v/>
       </c>
-      <c r="E56" s="32" t="str">
+      <c r="E56" s="31" t="str">
         <f>IF(AND(WBS入力!A56="",WBS入力!B56=""),"",IF(WBS入力!A56&lt;&gt;"","",IF(WBS入力!J56="","",WBS入力!J56)))</f>
         <v/>
       </c>
@@ -3328,11 +3317,11 @@
         <f>IF(AND(WBS入力!A57="",WBS入力!B57=""),"",IF(WBS入力!A57&lt;&gt;"","",WBS入力!D57))</f>
         <v/>
       </c>
-      <c r="D57" s="32" t="str">
+      <c r="D57" s="31" t="str">
         <f>IF(AND(WBS入力!A57="",WBS入力!B57=""),"",IF(WBS入力!A57&lt;&gt;"","",IF(WBS入力!E57="","",WBS入力!E57)))</f>
         <v/>
       </c>
-      <c r="E57" s="32" t="str">
+      <c r="E57" s="31" t="str">
         <f>IF(AND(WBS入力!A57="",WBS入力!B57=""),"",IF(WBS入力!A57&lt;&gt;"","",IF(WBS入力!J57="","",WBS入力!J57)))</f>
         <v/>
       </c>
@@ -3350,11 +3339,11 @@
         <f>IF(AND(WBS入力!A58="",WBS入力!B58=""),"",IF(WBS入力!A58&lt;&gt;"","",WBS入力!D58))</f>
         <v/>
       </c>
-      <c r="D58" s="32" t="str">
+      <c r="D58" s="31" t="str">
         <f>IF(AND(WBS入力!A58="",WBS入力!B58=""),"",IF(WBS入力!A58&lt;&gt;"","",IF(WBS入力!E58="","",WBS入力!E58)))</f>
         <v/>
       </c>
-      <c r="E58" s="32" t="str">
+      <c r="E58" s="31" t="str">
         <f>IF(AND(WBS入力!A58="",WBS入力!B58=""),"",IF(WBS入力!A58&lt;&gt;"","",IF(WBS入力!J58="","",WBS入力!J58)))</f>
         <v/>
       </c>
@@ -3372,11 +3361,11 @@
         <f>IF(AND(WBS入力!A59="",WBS入力!B59=""),"",IF(WBS入力!A59&lt;&gt;"","",WBS入力!D59))</f>
         <v/>
       </c>
-      <c r="D59" s="32" t="str">
+      <c r="D59" s="31" t="str">
         <f>IF(AND(WBS入力!A59="",WBS入力!B59=""),"",IF(WBS入力!A59&lt;&gt;"","",IF(WBS入力!E59="","",WBS入力!E59)))</f>
         <v/>
       </c>
-      <c r="E59" s="32" t="str">
+      <c r="E59" s="31" t="str">
         <f>IF(AND(WBS入力!A59="",WBS入力!B59=""),"",IF(WBS入力!A59&lt;&gt;"","",IF(WBS入力!J59="","",WBS入力!J59)))</f>
         <v/>
       </c>
@@ -3394,11 +3383,11 @@
         <f>IF(AND(WBS入力!A60="",WBS入力!B60=""),"",IF(WBS入力!A60&lt;&gt;"","",WBS入力!D60))</f>
         <v/>
       </c>
-      <c r="D60" s="32" t="str">
+      <c r="D60" s="31" t="str">
         <f>IF(AND(WBS入力!A60="",WBS入力!B60=""),"",IF(WBS入力!A60&lt;&gt;"","",IF(WBS入力!E60="","",WBS入力!E60)))</f>
         <v/>
       </c>
-      <c r="E60" s="32" t="str">
+      <c r="E60" s="31" t="str">
         <f>IF(AND(WBS入力!A60="",WBS入力!B60=""),"",IF(WBS入力!A60&lt;&gt;"","",IF(WBS入力!J60="","",WBS入力!J60)))</f>
         <v/>
       </c>
@@ -3416,11 +3405,11 @@
         <f>IF(AND(WBS入力!A61="",WBS入力!B61=""),"",IF(WBS入力!A61&lt;&gt;"","",WBS入力!D61))</f>
         <v/>
       </c>
-      <c r="D61" s="32" t="str">
+      <c r="D61" s="31" t="str">
         <f>IF(AND(WBS入力!A61="",WBS入力!B61=""),"",IF(WBS入力!A61&lt;&gt;"","",IF(WBS入力!E61="","",WBS入力!E61)))</f>
         <v/>
       </c>
-      <c r="E61" s="32" t="str">
+      <c r="E61" s="31" t="str">
         <f>IF(AND(WBS入力!A61="",WBS入力!B61=""),"",IF(WBS入力!A61&lt;&gt;"","",IF(WBS入力!J61="","",WBS入力!J61)))</f>
         <v/>
       </c>
@@ -3438,11 +3427,11 @@
         <f>IF(AND(WBS入力!A62="",WBS入力!B62=""),"",IF(WBS入力!A62&lt;&gt;"","",WBS入力!D62))</f>
         <v/>
       </c>
-      <c r="D62" s="32" t="str">
+      <c r="D62" s="31" t="str">
         <f>IF(AND(WBS入力!A62="",WBS入力!B62=""),"",IF(WBS入力!A62&lt;&gt;"","",IF(WBS入力!E62="","",WBS入力!E62)))</f>
         <v/>
       </c>
-      <c r="E62" s="32" t="str">
+      <c r="E62" s="31" t="str">
         <f>IF(AND(WBS入力!A62="",WBS入力!B62=""),"",IF(WBS入力!A62&lt;&gt;"","",IF(WBS入力!J62="","",WBS入力!J62)))</f>
         <v/>
       </c>
@@ -3460,11 +3449,11 @@
         <f>IF(AND(WBS入力!A63="",WBS入力!B63=""),"",IF(WBS入力!A63&lt;&gt;"","",WBS入力!D63))</f>
         <v/>
       </c>
-      <c r="D63" s="32" t="str">
+      <c r="D63" s="31" t="str">
         <f>IF(AND(WBS入力!A63="",WBS入力!B63=""),"",IF(WBS入力!A63&lt;&gt;"","",IF(WBS入力!E63="","",WBS入力!E63)))</f>
         <v/>
       </c>
-      <c r="E63" s="32" t="str">
+      <c r="E63" s="31" t="str">
         <f>IF(AND(WBS入力!A63="",WBS入力!B63=""),"",IF(WBS入力!A63&lt;&gt;"","",IF(WBS入力!J63="","",WBS入力!J63)))</f>
         <v/>
       </c>
@@ -3482,11 +3471,11 @@
         <f>IF(AND(WBS入力!A64="",WBS入力!B64=""),"",IF(WBS入力!A64&lt;&gt;"","",WBS入力!D64))</f>
         <v/>
       </c>
-      <c r="D64" s="32" t="str">
+      <c r="D64" s="31" t="str">
         <f>IF(AND(WBS入力!A64="",WBS入力!B64=""),"",IF(WBS入力!A64&lt;&gt;"","",IF(WBS入力!E64="","",WBS入力!E64)))</f>
         <v/>
       </c>
-      <c r="E64" s="32" t="str">
+      <c r="E64" s="31" t="str">
         <f>IF(AND(WBS入力!A64="",WBS入力!B64=""),"",IF(WBS入力!A64&lt;&gt;"","",IF(WBS入力!J64="","",WBS入力!J64)))</f>
         <v/>
       </c>
@@ -3504,11 +3493,11 @@
         <f>IF(AND(WBS入力!A65="",WBS入力!B65=""),"",IF(WBS入力!A65&lt;&gt;"","",WBS入力!D65))</f>
         <v/>
       </c>
-      <c r="D65" s="32" t="str">
+      <c r="D65" s="31" t="str">
         <f>IF(AND(WBS入力!A65="",WBS入力!B65=""),"",IF(WBS入力!A65&lt;&gt;"","",IF(WBS入力!E65="","",WBS入力!E65)))</f>
         <v/>
       </c>
-      <c r="E65" s="32" t="str">
+      <c r="E65" s="31" t="str">
         <f>IF(AND(WBS入力!A65="",WBS入力!B65=""),"",IF(WBS入力!A65&lt;&gt;"","",IF(WBS入力!J65="","",WBS入力!J65)))</f>
         <v/>
       </c>
@@ -3526,11 +3515,11 @@
         <f>IF(AND(WBS入力!A66="",WBS入力!B66=""),"",IF(WBS入力!A66&lt;&gt;"","",WBS入力!D66))</f>
         <v/>
       </c>
-      <c r="D66" s="32" t="str">
+      <c r="D66" s="31" t="str">
         <f>IF(AND(WBS入力!A66="",WBS入力!B66=""),"",IF(WBS入力!A66&lt;&gt;"","",IF(WBS入力!E66="","",WBS入力!E66)))</f>
         <v/>
       </c>
-      <c r="E66" s="32" t="str">
+      <c r="E66" s="31" t="str">
         <f>IF(AND(WBS入力!A66="",WBS入力!B66=""),"",IF(WBS入力!A66&lt;&gt;"","",IF(WBS入力!J66="","",WBS入力!J66)))</f>
         <v/>
       </c>
@@ -3548,11 +3537,11 @@
         <f>IF(AND(WBS入力!A67="",WBS入力!B67=""),"",IF(WBS入力!A67&lt;&gt;"","",WBS入力!D67))</f>
         <v/>
       </c>
-      <c r="D67" s="32" t="str">
+      <c r="D67" s="31" t="str">
         <f>IF(AND(WBS入力!A67="",WBS入力!B67=""),"",IF(WBS入力!A67&lt;&gt;"","",IF(WBS入力!E67="","",WBS入力!E67)))</f>
         <v/>
       </c>
-      <c r="E67" s="32" t="str">
+      <c r="E67" s="31" t="str">
         <f>IF(AND(WBS入力!A67="",WBS入力!B67=""),"",IF(WBS入力!A67&lt;&gt;"","",IF(WBS入力!J67="","",WBS入力!J67)))</f>
         <v/>
       </c>
@@ -3570,11 +3559,11 @@
         <f>IF(AND(WBS入力!A68="",WBS入力!B68=""),"",IF(WBS入力!A68&lt;&gt;"","",WBS入力!D68))</f>
         <v/>
       </c>
-      <c r="D68" s="32" t="str">
+      <c r="D68" s="31" t="str">
         <f>IF(AND(WBS入力!A68="",WBS入力!B68=""),"",IF(WBS入力!A68&lt;&gt;"","",IF(WBS入力!E68="","",WBS入力!E68)))</f>
         <v/>
       </c>
-      <c r="E68" s="32" t="str">
+      <c r="E68" s="31" t="str">
         <f>IF(AND(WBS入力!A68="",WBS入力!B68=""),"",IF(WBS入力!A68&lt;&gt;"","",IF(WBS入力!J68="","",WBS入力!J68)))</f>
         <v/>
       </c>
@@ -3592,11 +3581,11 @@
         <f>IF(AND(WBS入力!A69="",WBS入力!B69=""),"",IF(WBS入力!A69&lt;&gt;"","",WBS入力!D69))</f>
         <v/>
       </c>
-      <c r="D69" s="32" t="str">
+      <c r="D69" s="31" t="str">
         <f>IF(AND(WBS入力!A69="",WBS入力!B69=""),"",IF(WBS入力!A69&lt;&gt;"","",IF(WBS入力!E69="","",WBS入力!E69)))</f>
         <v/>
       </c>
-      <c r="E69" s="32" t="str">
+      <c r="E69" s="31" t="str">
         <f>IF(AND(WBS入力!A69="",WBS入力!B69=""),"",IF(WBS入力!A69&lt;&gt;"","",IF(WBS入力!J69="","",WBS入力!J69)))</f>
         <v/>
       </c>
@@ -3614,11 +3603,11 @@
         <f>IF(AND(WBS入力!A70="",WBS入力!B70=""),"",IF(WBS入力!A70&lt;&gt;"","",WBS入力!D70))</f>
         <v/>
       </c>
-      <c r="D70" s="32" t="str">
+      <c r="D70" s="31" t="str">
         <f>IF(AND(WBS入力!A70="",WBS入力!B70=""),"",IF(WBS入力!A70&lt;&gt;"","",IF(WBS入力!E70="","",WBS入力!E70)))</f>
         <v/>
       </c>
-      <c r="E70" s="32" t="str">
+      <c r="E70" s="31" t="str">
         <f>IF(AND(WBS入力!A70="",WBS入力!B70=""),"",IF(WBS入力!A70&lt;&gt;"","",IF(WBS入力!J70="","",WBS入力!J70)))</f>
         <v/>
       </c>
@@ -3636,11 +3625,11 @@
         <f>IF(AND(WBS入力!A71="",WBS入力!B71=""),"",IF(WBS入力!A71&lt;&gt;"","",WBS入力!D71))</f>
         <v/>
       </c>
-      <c r="D71" s="32" t="str">
+      <c r="D71" s="31" t="str">
         <f>IF(AND(WBS入力!A71="",WBS入力!B71=""),"",IF(WBS入力!A71&lt;&gt;"","",IF(WBS入力!E71="","",WBS入力!E71)))</f>
         <v/>
       </c>
-      <c r="E71" s="32" t="str">
+      <c r="E71" s="31" t="str">
         <f>IF(AND(WBS入力!A71="",WBS入力!B71=""),"",IF(WBS入力!A71&lt;&gt;"","",IF(WBS入力!J71="","",WBS入力!J71)))</f>
         <v/>
       </c>
@@ -3658,11 +3647,11 @@
         <f>IF(AND(WBS入力!A72="",WBS入力!B72=""),"",IF(WBS入力!A72&lt;&gt;"","",WBS入力!D72))</f>
         <v/>
       </c>
-      <c r="D72" s="32" t="str">
+      <c r="D72" s="31" t="str">
         <f>IF(AND(WBS入力!A72="",WBS入力!B72=""),"",IF(WBS入力!A72&lt;&gt;"","",IF(WBS入力!E72="","",WBS入力!E72)))</f>
         <v/>
       </c>
-      <c r="E72" s="32" t="str">
+      <c r="E72" s="31" t="str">
         <f>IF(AND(WBS入力!A72="",WBS入力!B72=""),"",IF(WBS入力!A72&lt;&gt;"","",IF(WBS入力!J72="","",WBS入力!J72)))</f>
         <v/>
       </c>
@@ -3680,11 +3669,11 @@
         <f>IF(AND(WBS入力!A73="",WBS入力!B73=""),"",IF(WBS入力!A73&lt;&gt;"","",WBS入力!D73))</f>
         <v/>
       </c>
-      <c r="D73" s="32" t="str">
+      <c r="D73" s="31" t="str">
         <f>IF(AND(WBS入力!A73="",WBS入力!B73=""),"",IF(WBS入力!A73&lt;&gt;"","",IF(WBS入力!E73="","",WBS入力!E73)))</f>
         <v/>
       </c>
-      <c r="E73" s="32" t="str">
+      <c r="E73" s="31" t="str">
         <f>IF(AND(WBS入力!A73="",WBS入力!B73=""),"",IF(WBS入力!A73&lt;&gt;"","",IF(WBS入力!J73="","",WBS入力!J73)))</f>
         <v/>
       </c>
@@ -3702,11 +3691,11 @@
         <f>IF(AND(WBS入力!A74="",WBS入力!B74=""),"",IF(WBS入力!A74&lt;&gt;"","",WBS入力!D74))</f>
         <v/>
       </c>
-      <c r="D74" s="32" t="str">
+      <c r="D74" s="31" t="str">
         <f>IF(AND(WBS入力!A74="",WBS入力!B74=""),"",IF(WBS入力!A74&lt;&gt;"","",IF(WBS入力!E74="","",WBS入力!E74)))</f>
         <v/>
       </c>
-      <c r="E74" s="32" t="str">
+      <c r="E74" s="31" t="str">
         <f>IF(AND(WBS入力!A74="",WBS入力!B74=""),"",IF(WBS入力!A74&lt;&gt;"","",IF(WBS入力!J74="","",WBS入力!J74)))</f>
         <v/>
       </c>
@@ -3724,11 +3713,11 @@
         <f>IF(AND(WBS入力!A75="",WBS入力!B75=""),"",IF(WBS入力!A75&lt;&gt;"","",WBS入力!D75))</f>
         <v/>
       </c>
-      <c r="D75" s="32" t="str">
+      <c r="D75" s="31" t="str">
         <f>IF(AND(WBS入力!A75="",WBS入力!B75=""),"",IF(WBS入力!A75&lt;&gt;"","",IF(WBS入力!E75="","",WBS入力!E75)))</f>
         <v/>
       </c>
-      <c r="E75" s="32" t="str">
+      <c r="E75" s="31" t="str">
         <f>IF(AND(WBS入力!A75="",WBS入力!B75=""),"",IF(WBS入力!A75&lt;&gt;"","",IF(WBS入力!J75="","",WBS入力!J75)))</f>
         <v/>
       </c>
@@ -3746,11 +3735,11 @@
         <f>IF(AND(WBS入力!A76="",WBS入力!B76=""),"",IF(WBS入力!A76&lt;&gt;"","",WBS入力!D76))</f>
         <v/>
       </c>
-      <c r="D76" s="32" t="str">
+      <c r="D76" s="31" t="str">
         <f>IF(AND(WBS入力!A76="",WBS入力!B76=""),"",IF(WBS入力!A76&lt;&gt;"","",IF(WBS入力!E76="","",WBS入力!E76)))</f>
         <v/>
       </c>
-      <c r="E76" s="32" t="str">
+      <c r="E76" s="31" t="str">
         <f>IF(AND(WBS入力!A76="",WBS入力!B76=""),"",IF(WBS入力!A76&lt;&gt;"","",IF(WBS入力!J76="","",WBS入力!J76)))</f>
         <v/>
       </c>
@@ -3768,11 +3757,11 @@
         <f>IF(AND(WBS入力!A77="",WBS入力!B77=""),"",IF(WBS入力!A77&lt;&gt;"","",WBS入力!D77))</f>
         <v/>
       </c>
-      <c r="D77" s="32" t="str">
+      <c r="D77" s="31" t="str">
         <f>IF(AND(WBS入力!A77="",WBS入力!B77=""),"",IF(WBS入力!A77&lt;&gt;"","",IF(WBS入力!E77="","",WBS入力!E77)))</f>
         <v/>
       </c>
-      <c r="E77" s="32" t="str">
+      <c r="E77" s="31" t="str">
         <f>IF(AND(WBS入力!A77="",WBS入力!B77=""),"",IF(WBS入力!A77&lt;&gt;"","",IF(WBS入力!J77="","",WBS入力!J77)))</f>
         <v/>
       </c>
@@ -3790,11 +3779,11 @@
         <f>IF(AND(WBS入力!A78="",WBS入力!B78=""),"",IF(WBS入力!A78&lt;&gt;"","",WBS入力!D78))</f>
         <v/>
       </c>
-      <c r="D78" s="32" t="str">
+      <c r="D78" s="31" t="str">
         <f>IF(AND(WBS入力!A78="",WBS入力!B78=""),"",IF(WBS入力!A78&lt;&gt;"","",IF(WBS入力!E78="","",WBS入力!E78)))</f>
         <v/>
       </c>
-      <c r="E78" s="32" t="str">
+      <c r="E78" s="31" t="str">
         <f>IF(AND(WBS入力!A78="",WBS入力!B78=""),"",IF(WBS入力!A78&lt;&gt;"","",IF(WBS入力!J78="","",WBS入力!J78)))</f>
         <v/>
       </c>
@@ -3812,11 +3801,11 @@
         <f>IF(AND(WBS入力!A79="",WBS入力!B79=""),"",IF(WBS入力!A79&lt;&gt;"","",WBS入力!D79))</f>
         <v/>
       </c>
-      <c r="D79" s="32" t="str">
+      <c r="D79" s="31" t="str">
         <f>IF(AND(WBS入力!A79="",WBS入力!B79=""),"",IF(WBS入力!A79&lt;&gt;"","",IF(WBS入力!E79="","",WBS入力!E79)))</f>
         <v/>
       </c>
-      <c r="E79" s="32" t="str">
+      <c r="E79" s="31" t="str">
         <f>IF(AND(WBS入力!A79="",WBS入力!B79=""),"",IF(WBS入力!A79&lt;&gt;"","",IF(WBS入力!J79="","",WBS入力!J79)))</f>
         <v/>
       </c>
@@ -3834,11 +3823,11 @@
         <f>IF(AND(WBS入力!A80="",WBS入力!B80=""),"",IF(WBS入力!A80&lt;&gt;"","",WBS入力!D80))</f>
         <v/>
       </c>
-      <c r="D80" s="32" t="str">
+      <c r="D80" s="31" t="str">
         <f>IF(AND(WBS入力!A80="",WBS入力!B80=""),"",IF(WBS入力!A80&lt;&gt;"","",IF(WBS入力!E80="","",WBS入力!E80)))</f>
         <v/>
       </c>
-      <c r="E80" s="32" t="str">
+      <c r="E80" s="31" t="str">
         <f>IF(AND(WBS入力!A80="",WBS入力!B80=""),"",IF(WBS入力!A80&lt;&gt;"","",IF(WBS入力!J80="","",WBS入力!J80)))</f>
         <v/>
       </c>
@@ -3856,11 +3845,11 @@
         <f>IF(AND(WBS入力!A81="",WBS入力!B81=""),"",IF(WBS入力!A81&lt;&gt;"","",WBS入力!D81))</f>
         <v/>
       </c>
-      <c r="D81" s="32" t="str">
+      <c r="D81" s="31" t="str">
         <f>IF(AND(WBS入力!A81="",WBS入力!B81=""),"",IF(WBS入力!A81&lt;&gt;"","",IF(WBS入力!E81="","",WBS入力!E81)))</f>
         <v/>
       </c>
-      <c r="E81" s="32" t="str">
+      <c r="E81" s="31" t="str">
         <f>IF(AND(WBS入力!A81="",WBS入力!B81=""),"",IF(WBS入力!A81&lt;&gt;"","",IF(WBS入力!J81="","",WBS入力!J81)))</f>
         <v/>
       </c>
@@ -3878,11 +3867,11 @@
         <f>IF(AND(WBS入力!A82="",WBS入力!B82=""),"",IF(WBS入力!A82&lt;&gt;"","",WBS入力!D82))</f>
         <v/>
       </c>
-      <c r="D82" s="32" t="str">
+      <c r="D82" s="31" t="str">
         <f>IF(AND(WBS入力!A82="",WBS入力!B82=""),"",IF(WBS入力!A82&lt;&gt;"","",IF(WBS入力!E82="","",WBS入力!E82)))</f>
         <v/>
       </c>
-      <c r="E82" s="32" t="str">
+      <c r="E82" s="31" t="str">
         <f>IF(AND(WBS入力!A82="",WBS入力!B82=""),"",IF(WBS入力!A82&lt;&gt;"","",IF(WBS入力!J82="","",WBS入力!J82)))</f>
         <v/>
       </c>
@@ -3900,11 +3889,11 @@
         <f>IF(AND(WBS入力!A83="",WBS入力!B83=""),"",IF(WBS入力!A83&lt;&gt;"","",WBS入力!D83))</f>
         <v/>
       </c>
-      <c r="D83" s="32" t="str">
+      <c r="D83" s="31" t="str">
         <f>IF(AND(WBS入力!A83="",WBS入力!B83=""),"",IF(WBS入力!A83&lt;&gt;"","",IF(WBS入力!E83="","",WBS入力!E83)))</f>
         <v/>
       </c>
-      <c r="E83" s="32" t="str">
+      <c r="E83" s="31" t="str">
         <f>IF(AND(WBS入力!A83="",WBS入力!B83=""),"",IF(WBS入力!A83&lt;&gt;"","",IF(WBS入力!J83="","",WBS入力!J83)))</f>
         <v/>
       </c>
@@ -3922,11 +3911,11 @@
         <f>IF(AND(WBS入力!A84="",WBS入力!B84=""),"",IF(WBS入力!A84&lt;&gt;"","",WBS入力!D84))</f>
         <v/>
       </c>
-      <c r="D84" s="32" t="str">
+      <c r="D84" s="31" t="str">
         <f>IF(AND(WBS入力!A84="",WBS入力!B84=""),"",IF(WBS入力!A84&lt;&gt;"","",IF(WBS入力!E84="","",WBS入力!E84)))</f>
         <v/>
       </c>
-      <c r="E84" s="32" t="str">
+      <c r="E84" s="31" t="str">
         <f>IF(AND(WBS入力!A84="",WBS入力!B84=""),"",IF(WBS入力!A84&lt;&gt;"","",IF(WBS入力!J84="","",WBS入力!J84)))</f>
         <v/>
       </c>
@@ -3944,11 +3933,11 @@
         <f>IF(AND(WBS入力!A85="",WBS入力!B85=""),"",IF(WBS入力!A85&lt;&gt;"","",WBS入力!D85))</f>
         <v/>
       </c>
-      <c r="D85" s="32" t="str">
+      <c r="D85" s="31" t="str">
         <f>IF(AND(WBS入力!A85="",WBS入力!B85=""),"",IF(WBS入力!A85&lt;&gt;"","",IF(WBS入力!E85="","",WBS入力!E85)))</f>
         <v/>
       </c>
-      <c r="E85" s="32" t="str">
+      <c r="E85" s="31" t="str">
         <f>IF(AND(WBS入力!A85="",WBS入力!B85=""),"",IF(WBS入力!A85&lt;&gt;"","",IF(WBS入力!J85="","",WBS入力!J85)))</f>
         <v/>
       </c>
@@ -3966,11 +3955,11 @@
         <f>IF(AND(WBS入力!A86="",WBS入力!B86=""),"",IF(WBS入力!A86&lt;&gt;"","",WBS入力!D86))</f>
         <v/>
       </c>
-      <c r="D86" s="32" t="str">
+      <c r="D86" s="31" t="str">
         <f>IF(AND(WBS入力!A86="",WBS入力!B86=""),"",IF(WBS入力!A86&lt;&gt;"","",IF(WBS入力!E86="","",WBS入力!E86)))</f>
         <v/>
       </c>
-      <c r="E86" s="32" t="str">
+      <c r="E86" s="31" t="str">
         <f>IF(AND(WBS入力!A86="",WBS入力!B86=""),"",IF(WBS入力!A86&lt;&gt;"","",IF(WBS入力!J86="","",WBS入力!J86)))</f>
         <v/>
       </c>
@@ -3988,11 +3977,11 @@
         <f>IF(AND(WBS入力!A87="",WBS入力!B87=""),"",IF(WBS入力!A87&lt;&gt;"","",WBS入力!D87))</f>
         <v/>
       </c>
-      <c r="D87" s="32" t="str">
+      <c r="D87" s="31" t="str">
         <f>IF(AND(WBS入力!A87="",WBS入力!B87=""),"",IF(WBS入力!A87&lt;&gt;"","",IF(WBS入力!E87="","",WBS入力!E87)))</f>
         <v/>
       </c>
-      <c r="E87" s="32" t="str">
+      <c r="E87" s="31" t="str">
         <f>IF(AND(WBS入力!A87="",WBS入力!B87=""),"",IF(WBS入力!A87&lt;&gt;"","",IF(WBS入力!J87="","",WBS入力!J87)))</f>
         <v/>
       </c>
@@ -4010,11 +3999,11 @@
         <f>IF(AND(WBS入力!A88="",WBS入力!B88=""),"",IF(WBS入力!A88&lt;&gt;"","",WBS入力!D88))</f>
         <v/>
       </c>
-      <c r="D88" s="32" t="str">
+      <c r="D88" s="31" t="str">
         <f>IF(AND(WBS入力!A88="",WBS入力!B88=""),"",IF(WBS入力!A88&lt;&gt;"","",IF(WBS入力!E88="","",WBS入力!E88)))</f>
         <v/>
       </c>
-      <c r="E88" s="32" t="str">
+      <c r="E88" s="31" t="str">
         <f>IF(AND(WBS入力!A88="",WBS入力!B88=""),"",IF(WBS入力!A88&lt;&gt;"","",IF(WBS入力!J88="","",WBS入力!J88)))</f>
         <v/>
       </c>
@@ -4032,11 +4021,11 @@
         <f>IF(AND(WBS入力!A89="",WBS入力!B89=""),"",IF(WBS入力!A89&lt;&gt;"","",WBS入力!D89))</f>
         <v/>
       </c>
-      <c r="D89" s="32" t="str">
+      <c r="D89" s="31" t="str">
         <f>IF(AND(WBS入力!A89="",WBS入力!B89=""),"",IF(WBS入力!A89&lt;&gt;"","",IF(WBS入力!E89="","",WBS入力!E89)))</f>
         <v/>
       </c>
-      <c r="E89" s="32" t="str">
+      <c r="E89" s="31" t="str">
         <f>IF(AND(WBS入力!A89="",WBS入力!B89=""),"",IF(WBS入力!A89&lt;&gt;"","",IF(WBS入力!J89="","",WBS入力!J89)))</f>
         <v/>
       </c>
@@ -4054,11 +4043,11 @@
         <f>IF(AND(WBS入力!A90="",WBS入力!B90=""),"",IF(WBS入力!A90&lt;&gt;"","",WBS入力!D90))</f>
         <v/>
       </c>
-      <c r="D90" s="32" t="str">
+      <c r="D90" s="31" t="str">
         <f>IF(AND(WBS入力!A90="",WBS入力!B90=""),"",IF(WBS入力!A90&lt;&gt;"","",IF(WBS入力!E90="","",WBS入力!E90)))</f>
         <v/>
       </c>
-      <c r="E90" s="32" t="str">
+      <c r="E90" s="31" t="str">
         <f>IF(AND(WBS入力!A90="",WBS入力!B90=""),"",IF(WBS入力!A90&lt;&gt;"","",IF(WBS入力!J90="","",WBS入力!J90)))</f>
         <v/>
       </c>
@@ -4076,11 +4065,11 @@
         <f>IF(AND(WBS入力!A91="",WBS入力!B91=""),"",IF(WBS入力!A91&lt;&gt;"","",WBS入力!D91))</f>
         <v/>
       </c>
-      <c r="D91" s="32" t="str">
+      <c r="D91" s="31" t="str">
         <f>IF(AND(WBS入力!A91="",WBS入力!B91=""),"",IF(WBS入力!A91&lt;&gt;"","",IF(WBS入力!E91="","",WBS入力!E91)))</f>
         <v/>
       </c>
-      <c r="E91" s="32" t="str">
+      <c r="E91" s="31" t="str">
         <f>IF(AND(WBS入力!A91="",WBS入力!B91=""),"",IF(WBS入力!A91&lt;&gt;"","",IF(WBS入力!J91="","",WBS入力!J91)))</f>
         <v/>
       </c>
@@ -4098,11 +4087,11 @@
         <f>IF(AND(WBS入力!A92="",WBS入力!B92=""),"",IF(WBS入力!A92&lt;&gt;"","",WBS入力!D92))</f>
         <v/>
       </c>
-      <c r="D92" s="32" t="str">
+      <c r="D92" s="31" t="str">
         <f>IF(AND(WBS入力!A92="",WBS入力!B92=""),"",IF(WBS入力!A92&lt;&gt;"","",IF(WBS入力!E92="","",WBS入力!E92)))</f>
         <v/>
       </c>
-      <c r="E92" s="32" t="str">
+      <c r="E92" s="31" t="str">
         <f>IF(AND(WBS入力!A92="",WBS入力!B92=""),"",IF(WBS入力!A92&lt;&gt;"","",IF(WBS入力!J92="","",WBS入力!J92)))</f>
         <v/>
       </c>
@@ -4120,11 +4109,11 @@
         <f>IF(AND(WBS入力!A93="",WBS入力!B93=""),"",IF(WBS入力!A93&lt;&gt;"","",WBS入力!D93))</f>
         <v/>
       </c>
-      <c r="D93" s="32" t="str">
+      <c r="D93" s="31" t="str">
         <f>IF(AND(WBS入力!A93="",WBS入力!B93=""),"",IF(WBS入力!A93&lt;&gt;"","",IF(WBS入力!E93="","",WBS入力!E93)))</f>
         <v/>
       </c>
-      <c r="E93" s="32" t="str">
+      <c r="E93" s="31" t="str">
         <f>IF(AND(WBS入力!A93="",WBS入力!B93=""),"",IF(WBS入力!A93&lt;&gt;"","",IF(WBS入力!J93="","",WBS入力!J93)))</f>
         <v/>
       </c>
@@ -4142,11 +4131,11 @@
         <f>IF(AND(WBS入力!A94="",WBS入力!B94=""),"",IF(WBS入力!A94&lt;&gt;"","",WBS入力!D94))</f>
         <v/>
       </c>
-      <c r="D94" s="32" t="str">
+      <c r="D94" s="31" t="str">
         <f>IF(AND(WBS入力!A94="",WBS入力!B94=""),"",IF(WBS入力!A94&lt;&gt;"","",IF(WBS入力!E94="","",WBS入力!E94)))</f>
         <v/>
       </c>
-      <c r="E94" s="32" t="str">
+      <c r="E94" s="31" t="str">
         <f>IF(AND(WBS入力!A94="",WBS入力!B94=""),"",IF(WBS入力!A94&lt;&gt;"","",IF(WBS入力!J94="","",WBS入力!J94)))</f>
         <v/>
       </c>
@@ -4164,11 +4153,11 @@
         <f>IF(AND(WBS入力!A95="",WBS入力!B95=""),"",IF(WBS入力!A95&lt;&gt;"","",WBS入力!D95))</f>
         <v/>
       </c>
-      <c r="D95" s="32" t="str">
+      <c r="D95" s="31" t="str">
         <f>IF(AND(WBS入力!A95="",WBS入力!B95=""),"",IF(WBS入力!A95&lt;&gt;"","",IF(WBS入力!E95="","",WBS入力!E95)))</f>
         <v/>
       </c>
-      <c r="E95" s="32" t="str">
+      <c r="E95" s="31" t="str">
         <f>IF(AND(WBS入力!A95="",WBS入力!B95=""),"",IF(WBS入力!A95&lt;&gt;"","",IF(WBS入力!J95="","",WBS入力!J95)))</f>
         <v/>
       </c>
@@ -4186,11 +4175,11 @@
         <f>IF(AND(WBS入力!A96="",WBS入力!B96=""),"",IF(WBS入力!A96&lt;&gt;"","",WBS入力!D96))</f>
         <v/>
       </c>
-      <c r="D96" s="32" t="str">
+      <c r="D96" s="31" t="str">
         <f>IF(AND(WBS入力!A96="",WBS入力!B96=""),"",IF(WBS入力!A96&lt;&gt;"","",IF(WBS入力!E96="","",WBS入力!E96)))</f>
         <v/>
       </c>
-      <c r="E96" s="32" t="str">
+      <c r="E96" s="31" t="str">
         <f>IF(AND(WBS入力!A96="",WBS入力!B96=""),"",IF(WBS入力!A96&lt;&gt;"","",IF(WBS入力!J96="","",WBS入力!J96)))</f>
         <v/>
       </c>
@@ -4208,11 +4197,11 @@
         <f>IF(AND(WBS入力!A97="",WBS入力!B97=""),"",IF(WBS入力!A97&lt;&gt;"","",WBS入力!D97))</f>
         <v/>
       </c>
-      <c r="D97" s="32" t="str">
+      <c r="D97" s="31" t="str">
         <f>IF(AND(WBS入力!A97="",WBS入力!B97=""),"",IF(WBS入力!A97&lt;&gt;"","",IF(WBS入力!E97="","",WBS入力!E97)))</f>
         <v/>
       </c>
-      <c r="E97" s="32" t="str">
+      <c r="E97" s="31" t="str">
         <f>IF(AND(WBS入力!A97="",WBS入力!B97=""),"",IF(WBS入力!A97&lt;&gt;"","",IF(WBS入力!J97="","",WBS入力!J97)))</f>
         <v/>
       </c>
@@ -4230,11 +4219,11 @@
         <f>IF(AND(WBS入力!A98="",WBS入力!B98=""),"",IF(WBS入力!A98&lt;&gt;"","",WBS入力!D98))</f>
         <v/>
       </c>
-      <c r="D98" s="32" t="str">
+      <c r="D98" s="31" t="str">
         <f>IF(AND(WBS入力!A98="",WBS入力!B98=""),"",IF(WBS入力!A98&lt;&gt;"","",IF(WBS入力!E98="","",WBS入力!E98)))</f>
         <v/>
       </c>
-      <c r="E98" s="32" t="str">
+      <c r="E98" s="31" t="str">
         <f>IF(AND(WBS入力!A98="",WBS入力!B98=""),"",IF(WBS入力!A98&lt;&gt;"","",IF(WBS入力!J98="","",WBS入力!J98)))</f>
         <v/>
       </c>
@@ -4252,11 +4241,11 @@
         <f>IF(AND(WBS入力!A99="",WBS入力!B99=""),"",IF(WBS入力!A99&lt;&gt;"","",WBS入力!D99))</f>
         <v/>
       </c>
-      <c r="D99" s="32" t="str">
+      <c r="D99" s="31" t="str">
         <f>IF(AND(WBS入力!A99="",WBS入力!B99=""),"",IF(WBS入力!A99&lt;&gt;"","",IF(WBS入力!E99="","",WBS入力!E99)))</f>
         <v/>
       </c>
-      <c r="E99" s="32" t="str">
+      <c r="E99" s="31" t="str">
         <f>IF(AND(WBS入力!A99="",WBS入力!B99=""),"",IF(WBS入力!A99&lt;&gt;"","",IF(WBS入力!J99="","",WBS入力!J99)))</f>
         <v/>
       </c>
@@ -4274,11 +4263,11 @@
         <f>IF(AND(WBS入力!A100="",WBS入力!B100=""),"",IF(WBS入力!A100&lt;&gt;"","",WBS入力!D100))</f>
         <v/>
       </c>
-      <c r="D100" s="32" t="str">
+      <c r="D100" s="31" t="str">
         <f>IF(AND(WBS入力!A100="",WBS入力!B100=""),"",IF(WBS入力!A100&lt;&gt;"","",IF(WBS入力!E100="","",WBS入力!E100)))</f>
         <v/>
       </c>
-      <c r="E100" s="32" t="str">
+      <c r="E100" s="31" t="str">
         <f>IF(AND(WBS入力!A100="",WBS入力!B100=""),"",IF(WBS入力!A100&lt;&gt;"","",IF(WBS入力!J100="","",WBS入力!J100)))</f>
         <v/>
       </c>
@@ -4310,28 +4299,18 @@
     <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
       <formula>"完了"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5:E100">
     <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
       <formula>"進行中"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5:E100">
     <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
       <formula>"遅延"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5:E100">
     <cfRule type="cellIs" dxfId="2" priority="6" operator="equal">
       <formula>"保留"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5:E100">
     <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
       <formula>"未着手"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5:E100">
     <cfRule type="cellIs" dxfId="0" priority="8" operator="equal">
       <formula>"中止"</formula>
     </cfRule>
